--- a/src/test/resources/testData/Attribute.xlsx
+++ b/src/test/resources/testData/Attribute.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkara\Desktop\workspace\EfecturaTestAutomation\src\test\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkara\Desktop\workspace\DiaPreProd\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FE9921-F9A3-4687-87EC-67CE4BD02CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A26805-FFAB-4E48-ABA7-B9230A534708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4296" yWindow="-10644" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/src/test/resources/testData/Attribute.xlsx
+++ b/src/test/resources/testData/Attribute.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkara\Desktop\workspace\DiaPreProd\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A26805-FFAB-4E48-ABA7-B9230A534708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48857FD8-5C79-46F4-9CC0-8E7DD4A028A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
